--- a/Result/profitability/2493.xlsx
+++ b/Result/profitability/2493.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.0875</v>
       </c>
       <c r="N2" t="n">
-        <v>30.65875</v>
+        <v>30.16</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>0.9475</v>
       </c>
       <c r="N3" t="n">
-        <v>29.955</v>
+        <v>29.60125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.80125</v>
+        <v>0.785</v>
       </c>
       <c r="N4" t="n">
-        <v>29.63375</v>
+        <v>29.43625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5725</v>
+        <v>0.6925</v>
       </c>
       <c r="N5" t="n">
-        <v>28.96875</v>
+        <v>28.6175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.49125</v>
+        <v>0.49625</v>
       </c>
       <c r="N6" t="n">
-        <v>25.35625</v>
+        <v>25.12</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3049999999999999</v>
+        <v>0.33125</v>
       </c>
       <c r="N7" t="n">
-        <v>24.395</v>
+        <v>24.3225</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0.14</v>
+        <v>0.15875</v>
       </c>
       <c r="N8" t="n">
-        <v>22.93</v>
+        <v>22.8625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2493</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1077</v>
+      </c>
+      <c r="D75" t="n">
+        <v>768</v>
+      </c>
+      <c r="E75" t="n">
+        <v>309</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>183</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>42</v>
+      </c>
+      <c r="J75" t="n">
+        <v>224</v>
+      </c>
+      <c r="K75" t="n">
+        <v>179</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.27875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.4275</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1190476190476191</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.5400000000000027</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01849948612538554</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.133333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.810000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08931977113795297</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
